--- a/table/resources/sample/common/Room_Bet.xlsx
+++ b/table/resources/sample/common/Room_Bet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Room_Bet" sheetId="18" r:id="rId1"/>
@@ -396,7 +396,7 @@
     <t>组合</t>
   </si>
   <si>
-    <t>0,13000,4000,5000</t>
+    <t>2000,13000,13000,0</t>
   </si>
   <si>
     <t>覆盖</t>
@@ -435,7 +435,7 @@
     <t>百家乐</t>
   </si>
   <si>
-    <t>1,13000,1200,1000</t>
+    <t>0,13000,15000,0</t>
   </si>
   <si>
     <t>三个骰子</t>
@@ -1661,8 +1661,8 @@
     <col min="2" max="2" width="12" style="3" customWidth="1"/>
     <col min="3" max="3" width="20.625" style="3" customWidth="1"/>
     <col min="4" max="4" width="8.625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="27.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="35.25" style="3" customWidth="1"/>
+    <col min="5" max="5" width="15.1416666666667" style="3" customWidth="1"/>
+    <col min="6" max="6" width="28.2333333333333" style="3" customWidth="1"/>
     <col min="7" max="7" width="8.625" style="3" customWidth="1"/>
     <col min="8" max="8" width="56.5" style="3" customWidth="1"/>
     <col min="9" max="9" width="8.875" style="3" customWidth="1"/>

--- a/table/resources/sample/common/Room_Bet.xlsx
+++ b/table/resources/sample/common/Room_Bet.xlsx
@@ -119,7 +119,8 @@
             <charset val="134"/>
           </rPr>
           <t>阶段信息:[准备阶段时间-毫秒，押分阶段时间-毫秒，亮牌阶段时间-毫秒，结算阶段-毫秒]
-2.时间: 毫秒</t>
+2.时间: 毫秒
+参考游戏荣耀中是有数到0得，而我们这没有，所以将时间加了1秒</t>
         </r>
       </text>
     </comment>
@@ -271,7 +272,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="66">
   <si>
     <t>游戏ID</t>
   </si>
@@ -396,7 +397,7 @@
     <t>组合</t>
   </si>
   <si>
-    <t>2000,13000,13000,0</t>
+    <t>2000,14000,11000,0</t>
   </si>
   <si>
     <t>覆盖</t>
@@ -420,22 +421,25 @@
     <t>直接</t>
   </si>
   <si>
+    <t>2000,14000,13000,0</t>
+  </si>
+  <si>
     <t>飞禽走兽</t>
   </si>
   <si>
-    <t>0,15000,16000,0</t>
+    <t>0,16000,17000,0</t>
   </si>
   <si>
     <t>豪车俱乐部</t>
   </si>
   <si>
-    <t>0,15000,11000,0</t>
+    <t>0,16000,12000,0</t>
   </si>
   <si>
     <t>百家乐</t>
   </si>
   <si>
-    <t>0,13000,15000,0</t>
+    <t>0,16000,14000,0</t>
   </si>
   <si>
     <t>三个骰子</t>
@@ -2080,7 +2084,7 @@
         <v>48</v>
       </c>
       <c r="K8" s="35" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="L8" s="3">
         <v>9700</v>
@@ -2143,7 +2147,7 @@
         <v>48</v>
       </c>
       <c r="K9" s="35" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="L9" s="3">
         <v>9700</v>
@@ -2206,7 +2210,7 @@
         <v>48</v>
       </c>
       <c r="K10" s="35" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="L10" s="3">
         <v>9700</v>
@@ -2245,7 +2249,7 @@
         <v>200300</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>36</v>
@@ -2269,7 +2273,7 @@
         <v>48</v>
       </c>
       <c r="K11" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L11" s="3">
         <v>9700</v>
@@ -2308,7 +2312,7 @@
         <v>200300</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>43</v>
@@ -2332,7 +2336,7 @@
         <v>48</v>
       </c>
       <c r="K12" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L12" s="3">
         <v>9700</v>
@@ -2371,7 +2375,7 @@
         <v>200300</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>45</v>
@@ -2395,7 +2399,7 @@
         <v>48</v>
       </c>
       <c r="K13" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L13" s="3">
         <v>9700</v>
@@ -2434,7 +2438,7 @@
         <v>200400</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>36</v>
@@ -2458,7 +2462,7 @@
         <v>48</v>
       </c>
       <c r="K14" s="35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L14" s="3">
         <v>9700</v>
@@ -2497,7 +2501,7 @@
         <v>200400</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>43</v>
@@ -2521,7 +2525,7 @@
         <v>48</v>
       </c>
       <c r="K15" s="35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L15" s="3">
         <v>9700</v>
@@ -2560,7 +2564,7 @@
         <v>200400</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>45</v>
@@ -2584,7 +2588,7 @@
         <v>48</v>
       </c>
       <c r="K16" s="35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L16" s="3">
         <v>9700</v>
@@ -2623,7 +2627,7 @@
         <v>200500</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>36</v>
@@ -2647,7 +2651,7 @@
         <v>40</v>
       </c>
       <c r="K17" s="35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L17" s="3">
         <v>9700</v>
@@ -2686,7 +2690,7 @@
         <v>200500</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>43</v>
@@ -2710,7 +2714,7 @@
         <v>40</v>
       </c>
       <c r="K18" s="35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L18" s="3">
         <v>9700</v>
@@ -2749,7 +2753,7 @@
         <v>200500</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>45</v>
@@ -2773,7 +2777,7 @@
         <v>40</v>
       </c>
       <c r="K19" s="35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L19" s="3">
         <v>9700</v>
@@ -2812,7 +2816,7 @@
         <v>200600</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>36</v>
@@ -2836,7 +2840,7 @@
         <v>48</v>
       </c>
       <c r="K20" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L20" s="3">
         <v>9700</v>
@@ -2875,7 +2879,7 @@
         <v>200600</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D21" s="17" t="s">
         <v>43</v>
@@ -2899,7 +2903,7 @@
         <v>48</v>
       </c>
       <c r="K21" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L21" s="3">
         <v>9700</v>
@@ -2938,7 +2942,7 @@
         <v>200600</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>45</v>
@@ -2962,7 +2966,7 @@
         <v>48</v>
       </c>
       <c r="K22" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L22" s="3">
         <v>9700</v>
@@ -3001,7 +3005,7 @@
         <v>200700</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>36</v>
@@ -3025,7 +3029,7 @@
         <v>48</v>
       </c>
       <c r="K23" s="35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L23" s="3">
         <v>9700</v>
@@ -3052,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:20">
@@ -3064,7 +3068,7 @@
         <v>200700</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D24" s="17" t="s">
         <v>43</v>
@@ -3088,7 +3092,7 @@
         <v>48</v>
       </c>
       <c r="K24" s="35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L24" s="3">
         <v>9700</v>
@@ -3115,7 +3119,7 @@
         <v>1</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" spans="1:20">
@@ -3127,7 +3131,7 @@
         <v>200700</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>45</v>
@@ -3151,7 +3155,7 @@
         <v>48</v>
       </c>
       <c r="K25" s="35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L25" s="3">
         <v>9700</v>
@@ -3178,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" spans="1:20">
@@ -3190,7 +3194,7 @@
         <v>200800</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D26" s="20" t="s">
         <v>36</v>
@@ -3214,7 +3218,7 @@
         <v>48</v>
       </c>
       <c r="K26" s="35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L26" s="3">
         <v>9700</v>
@@ -3253,7 +3257,7 @@
         <v>200800</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>43</v>
@@ -3277,7 +3281,7 @@
         <v>48</v>
       </c>
       <c r="K27" s="35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L27" s="3">
         <v>9700</v>
@@ -3316,7 +3320,7 @@
         <v>200800</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>45</v>
@@ -3340,7 +3344,7 @@
         <v>48</v>
       </c>
       <c r="K28" s="35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L28" s="3">
         <v>9700</v>
@@ -3379,7 +3383,7 @@
         <v>200900</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D29" s="19" t="s">
         <v>36</v>
@@ -3403,7 +3407,7 @@
         <v>48</v>
       </c>
       <c r="K29" s="35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L29" s="3">
         <v>9700</v>
@@ -3442,7 +3446,7 @@
         <v>200900</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D30" s="17" t="s">
         <v>43</v>
@@ -3466,7 +3470,7 @@
         <v>48</v>
       </c>
       <c r="K30" s="35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L30" s="3">
         <v>9700</v>
@@ -3505,7 +3509,7 @@
         <v>200900</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D31" s="24" t="s">
         <v>45</v>
@@ -3529,7 +3533,7 @@
         <v>48</v>
       </c>
       <c r="K31" s="35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L31" s="3">
         <v>9700</v>
@@ -3568,7 +3572,7 @@
         <v>201000</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D32" s="19" t="s">
         <v>36</v>
@@ -3577,7 +3581,7 @@
         <v>37</v>
       </c>
       <c r="F32" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G32" s="13">
         <v>1</v>
@@ -3592,7 +3596,7 @@
         <v>48</v>
       </c>
       <c r="K32" s="35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L32" s="3">
         <v>9700</v>
@@ -3631,7 +3635,7 @@
         <v>201000</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D33" s="17" t="s">
         <v>43</v>
@@ -3640,7 +3644,7 @@
         <v>37</v>
       </c>
       <c r="F33" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G33" s="17">
         <v>2</v>
@@ -3655,7 +3659,7 @@
         <v>48</v>
       </c>
       <c r="K33" s="35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L33" s="3">
         <v>9700</v>
@@ -3694,7 +3698,7 @@
         <v>201000</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D34" s="24" t="s">
         <v>45</v>
@@ -3703,7 +3707,7 @@
         <v>37</v>
       </c>
       <c r="F34" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G34" s="13">
         <v>3</v>
@@ -3718,7 +3722,7 @@
         <v>48</v>
       </c>
       <c r="K34" s="35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L34" s="3">
         <v>9700</v>

--- a/table/resources/sample/common/Room_Bet.xlsx
+++ b/table/resources/sample/common/Room_Bet.xlsx
@@ -367,7 +367,7 @@
     <t>TipText</t>
   </si>
   <si>
-    <t>EscText</t>
+    <t>EscTime</t>
   </si>
   <si>
     <t>EscTipText</t>
@@ -391,7 +391,7 @@
     <t>0:6:28|6:12:36|12:18:45|18:24:43</t>
   </si>
   <si>
-    <t>10,50,100,500,1000,5000,10000</t>
+    <t>100,200,500,1000,2000,5000,10000</t>
   </si>
   <si>
     <t>组合</t>
@@ -406,13 +406,13 @@
     <t>中级场</t>
   </si>
   <si>
-    <t>20000,5000,10000,20000,50000,100000,200000</t>
+    <t>10000,20000,50000,100000,200000,500000,1000000</t>
   </si>
   <si>
     <t>高级场</t>
   </si>
   <si>
-    <t>300000,500000,1000000,2000000,5000000,10000000,20000000</t>
+    <t>1000000,2000000,5000000,10000000,20000000,50000000,100000000</t>
   </si>
   <si>
     <t>龙虎斗</t>
@@ -1668,7 +1668,7 @@
     <col min="5" max="5" width="15.1416666666667" style="3" customWidth="1"/>
     <col min="6" max="6" width="28.2333333333333" style="3" customWidth="1"/>
     <col min="7" max="7" width="8.625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="56.5" style="3" customWidth="1"/>
+    <col min="8" max="8" width="65" style="3" customWidth="1"/>
     <col min="9" max="9" width="8.875" style="3" customWidth="1"/>
     <col min="10" max="10" width="5.125" style="3" customWidth="1"/>
     <col min="11" max="11" width="24.75" style="3" customWidth="1"/>
@@ -1679,7 +1679,7 @@
     <col min="21" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" customHeight="1" spans="1:20">
+    <row r="1" s="1" customFormat="1" ht="41" customHeight="1" spans="1:20">
       <c r="A1" s="6"/>
       <c r="B1" s="7" t="s">
         <v>0</v>
@@ -2282,7 +2282,7 @@
         <v>300</v>
       </c>
       <c r="N11" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O11" s="3">
         <v>15000</v>
@@ -2345,7 +2345,7 @@
         <v>300</v>
       </c>
       <c r="N12" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O12" s="3">
         <v>15000</v>
@@ -2408,7 +2408,7 @@
         <v>300</v>
       </c>
       <c r="N13" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O13" s="3">
         <v>15000</v>
@@ -2471,7 +2471,7 @@
         <v>300</v>
       </c>
       <c r="N14" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O14" s="3">
         <v>15000</v>
@@ -2534,7 +2534,7 @@
         <v>300</v>
       </c>
       <c r="N15" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O15" s="3">
         <v>15000</v>
@@ -2597,7 +2597,7 @@
         <v>300</v>
       </c>
       <c r="N16" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O16" s="3">
         <v>15000</v>
@@ -2660,7 +2660,7 @@
         <v>300</v>
       </c>
       <c r="N17" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O17" s="3">
         <v>15000</v>
@@ -2723,7 +2723,7 @@
         <v>300</v>
       </c>
       <c r="N18" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O18" s="3">
         <v>15000</v>
@@ -2786,7 +2786,7 @@
         <v>300</v>
       </c>
       <c r="N19" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O19" s="3">
         <v>15000</v>
@@ -2849,7 +2849,7 @@
         <v>300</v>
       </c>
       <c r="N20" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O20" s="3">
         <v>15000</v>
@@ -2912,7 +2912,7 @@
         <v>300</v>
       </c>
       <c r="N21" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O21" s="3">
         <v>15000</v>
@@ -2975,7 +2975,7 @@
         <v>300</v>
       </c>
       <c r="N22" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O22" s="3">
         <v>15000</v>
@@ -3038,7 +3038,7 @@
         <v>300</v>
       </c>
       <c r="N23" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O23" s="3">
         <v>15000</v>
@@ -3101,7 +3101,7 @@
         <v>300</v>
       </c>
       <c r="N24" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O24" s="3">
         <v>15000</v>
@@ -3164,7 +3164,7 @@
         <v>300</v>
       </c>
       <c r="N25" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O25" s="3">
         <v>15000</v>
@@ -3227,7 +3227,7 @@
         <v>300</v>
       </c>
       <c r="N26" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O26" s="3">
         <v>15000</v>
@@ -3290,7 +3290,7 @@
         <v>300</v>
       </c>
       <c r="N27" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O27" s="3">
         <v>15000</v>
@@ -3353,7 +3353,7 @@
         <v>300</v>
       </c>
       <c r="N28" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O28" s="3">
         <v>15000</v>
@@ -3416,7 +3416,7 @@
         <v>300</v>
       </c>
       <c r="N29" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O29" s="3">
         <v>15000</v>
@@ -3479,7 +3479,7 @@
         <v>300</v>
       </c>
       <c r="N30" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O30" s="3">
         <v>15000</v>
@@ -3542,7 +3542,7 @@
         <v>300</v>
       </c>
       <c r="N31" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O31" s="3">
         <v>15000</v>
@@ -3605,7 +3605,7 @@
         <v>300</v>
       </c>
       <c r="N32" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O32" s="3">
         <v>15000</v>
@@ -3668,7 +3668,7 @@
         <v>300</v>
       </c>
       <c r="N33" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O33" s="3">
         <v>15000</v>
@@ -3731,7 +3731,7 @@
         <v>300</v>
       </c>
       <c r="N34" s="3">
-        <v>60000</v>
+        <v>180000</v>
       </c>
       <c r="O34" s="3">
         <v>15000</v>

--- a/table/resources/sample/common/Room_Bet.xlsx
+++ b/table/resources/sample/common/Room_Bet.xlsx
@@ -1907,13 +1907,13 @@
         <v>60000</v>
       </c>
       <c r="O5" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P5" s="3">
         <v>15000</v>
       </c>
       <c r="Q5" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R5" s="4">
         <v>48</v>
@@ -1970,13 +1970,13 @@
         <v>60000</v>
       </c>
       <c r="O6" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P6" s="3">
         <v>15000</v>
       </c>
       <c r="Q6" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R6" s="4">
         <v>48</v>
@@ -2033,13 +2033,13 @@
         <v>60000</v>
       </c>
       <c r="O7" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P7" s="3">
         <v>15000</v>
       </c>
       <c r="Q7" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R7" s="4">
         <v>48</v>
@@ -2096,13 +2096,13 @@
         <v>60000</v>
       </c>
       <c r="O8" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P8" s="3">
         <v>15000</v>
       </c>
       <c r="Q8" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R8" s="4">
         <v>48</v>
@@ -2159,13 +2159,13 @@
         <v>60000</v>
       </c>
       <c r="O9" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P9" s="3">
         <v>15000</v>
       </c>
       <c r="Q9" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R9" s="4">
         <v>48</v>
@@ -2222,13 +2222,13 @@
         <v>60000</v>
       </c>
       <c r="O10" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P10" s="3">
         <v>15000</v>
       </c>
       <c r="Q10" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R10" s="4">
         <v>48</v>
@@ -2285,13 +2285,13 @@
         <v>180000</v>
       </c>
       <c r="O11" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P11" s="3">
         <v>15000</v>
       </c>
       <c r="Q11" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R11" s="4">
         <v>50</v>
@@ -2348,13 +2348,13 @@
         <v>180000</v>
       </c>
       <c r="O12" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P12" s="3">
         <v>15000</v>
       </c>
       <c r="Q12" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R12" s="4">
         <v>50</v>
@@ -2411,13 +2411,13 @@
         <v>180000</v>
       </c>
       <c r="O13" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P13" s="3">
         <v>15000</v>
       </c>
       <c r="Q13" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R13" s="4">
         <v>50</v>
@@ -2474,13 +2474,13 @@
         <v>180000</v>
       </c>
       <c r="O14" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P14" s="3">
         <v>15000</v>
       </c>
       <c r="Q14" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R14" s="4">
         <v>50</v>
@@ -2537,13 +2537,13 @@
         <v>180000</v>
       </c>
       <c r="O15" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P15" s="3">
         <v>15000</v>
       </c>
       <c r="Q15" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R15" s="4">
         <v>50</v>
@@ -2600,13 +2600,13 @@
         <v>180000</v>
       </c>
       <c r="O16" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P16" s="3">
         <v>15000</v>
       </c>
       <c r="Q16" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R16" s="4">
         <v>50</v>
@@ -2663,13 +2663,13 @@
         <v>180000</v>
       </c>
       <c r="O17" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P17" s="3">
         <v>15000</v>
       </c>
       <c r="Q17" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R17" s="4">
         <v>48</v>
@@ -2726,13 +2726,13 @@
         <v>180000</v>
       </c>
       <c r="O18" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P18" s="3">
         <v>15000</v>
       </c>
       <c r="Q18" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R18" s="4">
         <v>48</v>
@@ -2789,13 +2789,13 @@
         <v>180000</v>
       </c>
       <c r="O19" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P19" s="3">
         <v>15000</v>
       </c>
       <c r="Q19" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R19" s="4">
         <v>48</v>
@@ -2852,13 +2852,13 @@
         <v>180000</v>
       </c>
       <c r="O20" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P20" s="3">
         <v>15000</v>
       </c>
       <c r="Q20" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R20" s="4">
         <v>500</v>
@@ -2915,13 +2915,13 @@
         <v>180000</v>
       </c>
       <c r="O21" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P21" s="3">
         <v>15000</v>
       </c>
       <c r="Q21" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R21" s="4">
         <v>500</v>
@@ -2978,13 +2978,13 @@
         <v>180000</v>
       </c>
       <c r="O22" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P22" s="3">
         <v>15000</v>
       </c>
       <c r="Q22" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R22" s="4">
         <v>500</v>
@@ -3041,13 +3041,13 @@
         <v>180000</v>
       </c>
       <c r="O23" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P23" s="3">
         <v>15000</v>
       </c>
       <c r="Q23" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R23" s="4">
         <v>30</v>
@@ -3104,13 +3104,13 @@
         <v>180000</v>
       </c>
       <c r="O24" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P24" s="3">
         <v>15000</v>
       </c>
       <c r="Q24" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R24" s="4">
         <v>30</v>
@@ -3167,13 +3167,13 @@
         <v>180000</v>
       </c>
       <c r="O25" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P25" s="3">
         <v>15000</v>
       </c>
       <c r="Q25" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R25" s="4">
         <v>30</v>
@@ -3230,13 +3230,13 @@
         <v>180000</v>
       </c>
       <c r="O26" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P26" s="3">
         <v>15000</v>
       </c>
       <c r="Q26" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R26" s="4">
         <v>500</v>
@@ -3293,13 +3293,13 @@
         <v>180000</v>
       </c>
       <c r="O27" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P27" s="3">
         <v>15000</v>
       </c>
       <c r="Q27" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R27" s="4">
         <v>500</v>
@@ -3356,13 +3356,13 @@
         <v>180000</v>
       </c>
       <c r="O28" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P28" s="3">
         <v>15000</v>
       </c>
       <c r="Q28" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R28" s="4">
         <v>500</v>
@@ -3419,13 +3419,13 @@
         <v>180000</v>
       </c>
       <c r="O29" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P29" s="3">
         <v>15000</v>
       </c>
       <c r="Q29" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R29" s="4">
         <v>500</v>
@@ -3482,13 +3482,13 @@
         <v>180000</v>
       </c>
       <c r="O30" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P30" s="3">
         <v>15000</v>
       </c>
       <c r="Q30" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R30" s="4">
         <v>500</v>
@@ -3545,13 +3545,13 @@
         <v>180000</v>
       </c>
       <c r="O31" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P31" s="3">
         <v>15000</v>
       </c>
       <c r="Q31" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R31" s="4">
         <v>500</v>
@@ -3608,13 +3608,13 @@
         <v>180000</v>
       </c>
       <c r="O32" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P32" s="3">
         <v>15000</v>
       </c>
       <c r="Q32" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R32" s="4">
         <v>50</v>
@@ -3671,13 +3671,13 @@
         <v>180000</v>
       </c>
       <c r="O33" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P33" s="3">
         <v>15000</v>
       </c>
       <c r="Q33" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R33" s="4">
         <v>50</v>
@@ -3734,13 +3734,13 @@
         <v>180000</v>
       </c>
       <c r="O34" s="3">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="P34" s="3">
         <v>15000</v>
       </c>
       <c r="Q34" s="38">
-        <v>15001</v>
+        <v>16008</v>
       </c>
       <c r="R34" s="4">
         <v>50</v>
